--- a/lead_generation_forms/026_loyalty_personalization_ai_registration_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/026_loyalty_personalization_ai_registration_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'increase_revenue'}</t>
+          <t>increase_revenue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Increase revenue'}</t>
+          <t>Increase revenue</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'acquire_new_customers'}</t>
+          <t>acquire_new_customers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Acquire new customers'}</t>
+          <t>Acquire new customers</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'improve_customer_experience'}</t>
+          <t>improve_customer_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Improve customer experience'}</t>
+          <t>Improve customer experience</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'ai-powered_loyalty_programs'}</t>
+          <t>ai-powered_loyalty_programs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'AI-powered loyalty programs'}</t>
+          <t>AI-powered loyalty programs</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'ai-driven_customer_experience'}</t>
+          <t>ai-driven_customer_experience</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'AI-driven customer experience'}</t>
+          <t>AI-driven customer experience</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'ai-based_loyalty_programs'}</t>
+          <t>ai-based_loyalty_programs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'AI-based loyalty programs'}</t>
+          <t>AI-based loyalty programs</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'adobe'}</t>
+          <t>adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Adobe'}</t>
+          <t>Adobe</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'hubspot'}</t>
+          <t>hubspot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'HubSpot'}</t>
+          <t>HubSpot</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'1-10_employees'}</t>
+          <t>1-10_employees</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': '1-10 employees'}</t>
+          <t>1-10 employees</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'11-50_employees'}</t>
+          <t>11-50_employees</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': '11-50 employees'}</t>
+          <t>11-50 employees</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'51-100_employees'}</t>
+          <t>51-100_employees</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': '51-100 employees'}</t>
+          <t>51-100 employees</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'101+_employees'}</t>
+          <t>101+_employees</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': '101+ employees'}</t>
+          <t>101+ employees</t>
         </is>
       </c>
     </row>
